--- a/data/Categorized.xlsx
+++ b/data/Categorized.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/strahinja/Desktop/TFM/Research papers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljaljevi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F96BEA-D192-2F4E-BEAF-5950EC533CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4187EC-9CB8-44D4-ABEC-77A2926E67E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1100" windowWidth="34040" windowHeight="19480" activeTab="1" xr2:uid="{EABBDD19-FCDE-D54F-AC89-1FBD5D5097D3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EABBDD19-FCDE-D54F-AC89-1FBD5D5097D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Papers" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId3"/>
+    <pivotCache cacheId="13" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="113">
   <si>
     <t>Can Large Language Models Write Parallel Code?</t>
   </si>
@@ -273,6 +273,123 @@
   </si>
   <si>
     <t>Count of Title</t>
+  </si>
+  <si>
+    <t>Leveraging Large Language Models for Code Translation and Software Development in Scientific Computing</t>
+  </si>
+  <si>
+    <t>DhruvDubey2025CodeTranslation</t>
+  </si>
+  <si>
+    <t>Dhruv, Akash and Dubey, Anshu</t>
+  </si>
+  <si>
+    <t>Fortran2CPP: Automating Fortran-to-C++ Translation using LLMs via Multi-Turn Dialogue and Dual-Agent Integration</t>
+  </si>
+  <si>
+    <t>Chen2024Fortran2CPP</t>
+  </si>
+  <si>
+    <t>Le Chen and Bin Lei and Dunzhi Zhou and Pei{-}Hung Lin and Chunhua Liao and Caiwen Ding and Ali Jannesari</t>
+  </si>
+  <si>
+    <t>ChatHPC: Building the Foundations for a Productive and Trustworthy AI-Assisted HPC Ecosystem</t>
+  </si>
+  <si>
+    <t>ValeroLara2025ChatHPC</t>
+  </si>
+  <si>
+    <t>Pedro Valero Lara and Aaron Young and Jeffrey S. Vetter and Zheming Jin and Swaroop Pophale and Mohammad Alaul Haque Monil and Keita Teranishi and William F. Godoy</t>
+  </si>
+  <si>
+    <t>ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads</t>
+  </si>
+  <si>
+    <t>ValeroLara2026ChatMPI</t>
+  </si>
+  <si>
+    <t>Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy</t>
+  </si>
+  <si>
+    <t>{PRAGMA}: A Profiling-Reasoned Multi-Agent Framework for Automatic Kernel Optimization</t>
+  </si>
+  <si>
+    <t>Lei2025PRAGMA</t>
+  </si>
+  <si>
+    <t>Kelun Lei and Hailong Yang and Huaitao Zhang and Xin You and Kaige Zhang and Zhongzhi Luan and Yi Liu and Depei Qian</t>
+  </si>
+  <si>
+    <t>Leveraging LLMs to Automate Energy-Aware Refactoring of Parallel Scientific Codes</t>
+  </si>
+  <si>
+    <t>Dearing2025LASSIEE</t>
+  </si>
+  <si>
+    <t>Matthew T. Dearing and Yiheng Tao and Xingfu Wu and Zhiling Lan and Valerie Taylor</t>
+  </si>
+  <si>
+    <t>LLM-HPC++: Evaluating LLM-Generated Modern C++ and MPI+OpenMP Codes for Scalable Mandelbrot Set Computation</t>
+  </si>
+  <si>
+    <t>Diehl2025LLMHPCpp</t>
+  </si>
+  <si>
+    <t>Patrick Diehl and Noujoud Nader and Deepti Gupta</t>
+  </si>
+  <si>
+    <t>Adding New Capability in Existing Scientific Application with LLM Assistance</t>
+  </si>
+  <si>
+    <t>DubeyDhruv2025NewCapability</t>
+  </si>
+  <si>
+    <t>Anshu Dubey and Akash Dhruv</t>
+  </si>
+  <si>
+    <t>{PEAK}: A Performance Engineering AI-Assistant for GPU Kernels Powered by Natural Language Transformations</t>
+  </si>
+  <si>
+    <t>Tariq2025PEAK</t>
+  </si>
+  <si>
+    <t>Muhammad Usman Tariq and Abhinav Jangda and Angelica Moreira and Madan Musuvathi and Tyler Sorensen</t>
+  </si>
+  <si>
+    <t>Chat{PORT}: Fine-Tuned {LLM} for Easy Code {PORT}ing</t>
+  </si>
+  <si>
+    <t>Pophale2026ChatPORT</t>
+  </si>
+  <si>
+    <t>Swaroop Pophale and Zheming Jin and Keita Teranishi</t>
+  </si>
+  <si>
+    <t>Enhancing Chat{PORT} with {CUDA}-to-{SYCL} Kernel Translation Capability</t>
+  </si>
+  <si>
+    <t>Jin2025ChatPORTCudaSyCL</t>
+  </si>
+  <si>
+    <t>Zheming Jin and Swaroop Pophale and Keita Teranishi</t>
+  </si>
+  <si>
+    <t>{PCEBench}: A Multi-Dimensional Benchmark for Evaluating Large Language Models in Parallel Code Generation</t>
+  </si>
+  <si>
+    <t>Chen2025PCEBench</t>
+  </si>
+  <si>
+    <t>L. Chen and N. Ahmed and M. Capot{\u{a}} and T. Willke and N. Hasabnis and A. Jannesari</t>
+  </si>
+  <si>
+    <t>{UniPar}: A Unified LLM-Based Framework for Parallel and Accelerated Code Translation in {HPC}</t>
+  </si>
+  <si>
+    <t>Bitan2025UniPar</t>
+  </si>
+  <si>
+    <t>Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren</t>
   </si>
 </sst>
 </file>
@@ -317,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
@@ -325,11 +442,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Times New Roman"/>
@@ -739,19 +941,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -853,7 +1055,6 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
@@ -1468,9 +1669,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Strahinja Ljaljevic" refreshedDate="45842.573795717595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="27" xr:uid="{EFD9FE8D-7D09-9643-9262-DAD621E40C4B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ljaljevic, Strahinja" refreshedDate="46141.410085995369" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{DB901785-669C-49A0-8F65-FBC058EF8B51}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G28" sheet="Papers"/>
+    <worksheetSource ref="A1:G51" sheet="Papers"/>
   </cacheSource>
   <cacheFields count="7">
     <cacheField name="Title" numFmtId="0">
@@ -1483,7 +1684,7 @@
       <sharedItems longText="1"/>
     </cacheField>
     <cacheField name="Year" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2025-06-29T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-01T00:00:00" maxDate="2026-01-26T00:00:00"/>
     </cacheField>
     <cacheField name="PaperType" numFmtId="0">
       <sharedItems/>
@@ -1492,12 +1693,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
-      <sharedItems count="5">
+      <sharedItems count="6">
         <s v="Challenges &amp; Landscape"/>
         <s v="Evaluation &amp; Benchmarking"/>
         <s v="Code Generation"/>
         <s v="Parallelization &amp; Optimization"/>
         <s v="Frameworks &amp; Architectures"/>
+        <s v="Evaluation &amp; Benchmarking " u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -1510,7 +1712,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
   <r>
     <s v="The Landscape and Challenges of HPC Research and LLMs"/>
     <s v="chen_landscape_2024"/>
@@ -1749,16 +1951,223 @@
     <s v="LLM &amp; HPC:Benchmarking DeepSeek's Performance in High-Performance Computing Tasks"/>
     <s v="nader2025llmhpcbenchmarkingdeepseeks"/>
     <s v="Noujoud Nader, Patrick Diehl, Steve Brandt, Hartmut Kaiser"/>
-    <d v="2025-03-15T00:00:00"/>
+    <d v="2025-04-28T00:00:00"/>
     <s v="Main Research Paper"/>
     <s v="Y"/>
     <x v="1"/>
+  </r>
+  <r>
+    <s v="Leveraging Large Language Models for Code Translation and Software Development in Scientific Computing"/>
+    <s v="DhruvDubey2025CodeTranslation"/>
+    <s v="Dhruv, Akash and Dubey, Anshu"/>
+    <d v="2025-06-01T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="Leveraging Large Language Models for Code Translation and Software Development in Scientific Computing"/>
+    <s v="DhruvDubey2025CodeTranslation"/>
+    <s v="Dhruv, Akash and Dubey, Anshu"/>
+    <d v="2025-06-01T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Fortran2CPP: Automating Fortran-to-C++ Translation using LLMs via Multi-Turn Dialogue and Dual-Agent Integration"/>
+    <s v="Chen2024Fortran2CPP"/>
+    <s v="Le Chen and Bin Lei and Dunzhi Zhou and Pei{-}Hung Lin and Chunhua Liao and Caiwen Ding and Ali Jannesari"/>
+    <d v="2024-12-27T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="ChatHPC: Building the Foundations for a Productive and Trustworthy AI-Assisted HPC Ecosystem"/>
+    <s v="ValeroLara2025ChatHPC"/>
+    <s v="Pedro Valero Lara and Aaron Young and Jeffrey S. Vetter and Zheming Jin and Swaroop Pophale and Mohammad Alaul Haque Monil and Keita Teranishi and William F. Godoy"/>
+    <d v="2025-11-15T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads"/>
+    <s v="ValeroLara2026ChatMPI"/>
+    <s v="Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy"/>
+    <d v="2026-01-25T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads"/>
+    <s v="ValeroLara2026ChatMPI"/>
+    <s v="Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy"/>
+    <d v="2026-01-25T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="ChatMPI: LLM-Driven MPI Code Generation for HPC Workloads"/>
+    <s v="ValeroLara2026ChatMPI"/>
+    <s v="Pedro Valero-Lara and Aaron Young and Thomas Naughton III and Christian Engelmann and Al Geist and Jeffrey S. Vetter and Keita Teranishi and William F. Godoy"/>
+    <d v="2026-01-25T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="{PRAGMA}: A Profiling-Reasoned Multi-Agent Framework for Automatic Kernel Optimization"/>
+    <s v="Lei2025PRAGMA"/>
+    <s v="Kelun Lei and Hailong Yang and Huaitao Zhang and Xin You and Kaige Zhang and Zhongzhi Luan and Yi Liu and Depei Qian"/>
+    <d v="2025-11-09T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="{PRAGMA}: A Profiling-Reasoned Multi-Agent Framework for Automatic Kernel Optimization"/>
+    <s v="Lei2025PRAGMA"/>
+    <s v="Kelun Lei and Hailong Yang and Huaitao Zhang and Xin You and Kaige Zhang and Zhongzhi Luan and Yi Liu and Depei Qian"/>
+    <d v="2025-11-09T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="Leveraging LLMs to Automate Energy-Aware Refactoring of Parallel Scientific Codes"/>
+    <s v="Dearing2025LASSIEE"/>
+    <s v="Matthew T. Dearing and Yiheng Tao and Xingfu Wu and Zhiling Lan and Valerie Taylor"/>
+    <d v="2025-05-04T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="LLM-HPC++: Evaluating LLM-Generated Modern C++ and MPI+OpenMP Codes for Scalable Mandelbrot Set Computation"/>
+    <s v="Diehl2025LLMHPCpp"/>
+    <s v="Patrick Diehl and Noujoud Nader and Deepti Gupta"/>
+    <d v="2025-12-18T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LLM-HPC++: Evaluating LLM-Generated Modern C++ and MPI+OpenMP Codes for Scalable Mandelbrot Set Computation"/>
+    <s v="Diehl2025LLMHPCpp"/>
+    <s v="Patrick Diehl and Noujoud Nader and Deepti Gupta"/>
+    <d v="2025-12-18T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="Adding New Capability in Existing Scientific Application with LLM Assistance"/>
+    <s v="DubeyDhruv2025NewCapability"/>
+    <s v="Anshu Dubey and Akash Dhruv"/>
+    <d v="2025-10-30T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="Adding New Capability in Existing Scientific Application with LLM Assistance"/>
+    <s v="DubeyDhruv2025NewCapability"/>
+    <s v="Anshu Dubey and Akash Dhruv"/>
+    <d v="2025-10-30T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="{PEAK}: A Performance Engineering AI-Assistant for GPU Kernels Powered by Natural Language Transformations"/>
+    <s v="Tariq2025PEAK"/>
+    <s v="Muhammad Usman Tariq and Abhinav Jangda and Angelica Moreira and Madan Musuvathi and Tyler Sorensen"/>
+    <d v="2025-12-22T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="{PEAK}: A Performance Engineering AI-Assistant for GPU Kernels Powered by Natural Language Transformations"/>
+    <s v="Tariq2025PEAK"/>
+    <s v="Muhammad Usman Tariq and Abhinav Jangda and Angelica Moreira and Madan Musuvathi and Tyler Sorensen"/>
+    <d v="2025-12-22T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="Chat{PORT}: Fine-Tuned {LLM} for Easy Code {PORT}ing"/>
+    <s v="Pophale2026ChatPORT"/>
+    <s v="Swaroop Pophale and Zheming Jin and Keita Teranishi"/>
+    <d v="2025-09-29T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="Chat{PORT}: Fine-Tuned {LLM} for Easy Code {PORT}ing"/>
+    <s v="Pophale2026ChatPORT"/>
+    <s v="Swaroop Pophale and Zheming Jin and Keita Teranishi"/>
+    <d v="2025-09-29T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="Enhancing Chat{PORT} with {CUDA}-to-{SYCL} Kernel Translation Capability"/>
+    <s v="Jin2025ChatPORTCudaSyCL"/>
+    <s v="Zheming Jin and Swaroop Pophale and Keita Teranishi"/>
+    <d v="2025-11-15T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="Enhancing Chat{PORT} with {CUDA}-to-{SYCL} Kernel Translation Capability"/>
+    <s v="Jin2025ChatPORTCudaSyCL"/>
+    <s v="Zheming Jin and Swaroop Pophale and Keita Teranishi"/>
+    <d v="2025-11-15T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="{PCEBench}: A Multi-Dimensional Benchmark for Evaluating Large Language Models in Parallel Code Generation"/>
+    <s v="Chen2025PCEBench"/>
+    <s v="L. Chen and N. Ahmed and M. Capot{\u{a}} and T. Willke and N. Hasabnis and A. Jannesari"/>
+    <d v="2025-07-23T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="{UniPar}: A Unified LLM-Based Framework for Parallel and Accelerated Code Translation in {HPC}"/>
+    <s v="Bitan2025UniPar"/>
+    <s v="Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren"/>
+    <d v="2025-09-15T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="{UniPar}: A Unified LLM-Based Framework for Parallel and Accelerated Code Translation in {HPC}"/>
+    <s v="Bitan2025UniPar"/>
+    <s v="Tomer Bitan and Tal Kadosh and Erel Kaplan and Shira Meiri and Le Chen and Peter Morales and Niranjan Hasabnis and Gal Oren"/>
+    <d v="2025-09-15T00:00:00"/>
+    <s v="Main Research Paper"/>
+    <s v="Y"/>
+    <x v="4"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{023562C1-3C04-D84F-AC87-AFCF307234F4}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2882EFEC-9925-4453-9693-68EA67E64703}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21">
   <location ref="C7:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
@@ -1768,12 +2177,13 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="6">
+      <items count="7">
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="1"/>
         <item x="0"/>
+        <item m="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1808,26 +2218,26 @@
     <dataField name="Count of Title" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="5">
+    <format dxfId="0">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -2231,19 +2641,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FFA343-EB2A-1B45-BE4C-A6BBDF20CD94}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="81.5" customWidth="1"/>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.375" customWidth="1"/>
     <col min="3" max="3" width="75" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="18.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2266,7 +2676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2289,7 +2699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2312,7 +2722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2335,7 +2745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2358,7 +2768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2381,7 +2791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -2404,7 +2814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2427,7 +2837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2450,7 +2860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2473,7 +2883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2496,7 +2906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2519,7 +2929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -2542,7 +2952,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -2565,7 +2975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -2588,7 +2998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -2611,7 +3021,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2634,7 +3044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -2657,7 +3067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2680,7 +3090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -2703,7 +3113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2726,7 +3136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2749,7 +3159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2772,7 +3182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -2795,7 +3205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2818,7 +3228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -2841,7 +3251,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -2864,7 +3274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -2885,6 +3295,535 @@
       </c>
       <c r="G28" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45809</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="1">
+        <v>45809</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="1">
+        <v>45653</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="1">
+        <v>45976</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46047</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46047</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="1">
+        <v>46047</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="1">
+        <v>45970</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="1">
+        <v>45970</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="1">
+        <v>45781</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="1">
+        <v>46009</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="1">
+        <v>46009</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="1">
+        <v>45960</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="1">
+        <v>45960</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="1">
+        <v>46013</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="1">
+        <v>46013</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="1">
+        <v>45929</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="1">
+        <v>45929</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="1">
+        <v>45976</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="1">
+        <v>45976</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="1">
+        <v>45861</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="1">
+        <v>45915</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="1">
+        <v>45915</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2895,16 +3834,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC25FC43-2080-744B-ABBC-B9BDA7910DE8}">
-  <dimension ref="C7:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="C7:D14"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="3"/>
-    <col min="3" max="3" width="25.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="2" width="10.875" style="3"/>
+    <col min="3" max="3" width="27.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
@@ -2912,53 +3851,57 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D8" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D9" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="3">
-        <v>27</v>
-      </c>
+      <c r="D13" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14"/>
+      <c r="D14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
